--- a/artfynd/A 43379-2022 artfynd.xlsx
+++ b/artfynd/A 43379-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43379-2022 artfynd.xlsx
+++ b/artfynd/A 43379-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114594526</v>
+        <v>113173086</v>
       </c>
       <c r="B2" t="n">
-        <v>57943</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,14 +709,10 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -731,17 +722,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergskanten, Löftabro, Stråvalla, Hl</t>
+          <t>Kapelliden skogskant, Löftabro, Stråvalla, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>330178</v>
+        <v>330173</v>
       </c>
       <c r="R2" t="n">
-        <v>6355294</v>
+        <v>6355351</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,27 +756,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Besöker fågelbord.</t>
+          <t>Duvhöken flyger över skogskanten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -812,37 +803,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114594546</v>
+        <v>127904343</v>
       </c>
       <c r="B3" t="n">
-        <v>57885</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103042</v>
+        <v>100053</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -850,11 +836,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>rastande</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -864,14 +848,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergskanten, Löftabro, Stråvalla, Hl</t>
+          <t>Kapelliden, 439 62 Löftaskog, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>330178</v>
+        <v>330149</v>
       </c>
       <c r="R3" t="n">
-        <v>6355294</v>
+        <v>6355350</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -898,27 +882,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Besöker fågelbord.</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,44 +908,1223 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Buskar</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>numera kalhuggen lövskog med enar. Närhet till tallar och ett område med granskog.Kontakt med ett område med tall- och blandskog.</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>enar</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Juniperus</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Juniperus</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Johan Möller</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>106851322</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56895</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100088</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Natrix natrix</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Berskanten, Löftabro, Löftabro, Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>330185</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6355281</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-08-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-08-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rörde sig på gräset utanför huset på väg mot skogen.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Antti Friberg</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Antti Friberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>106850985</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>bergskanten, Löftabro, Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>330185</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6355281</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-04-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-04-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gammal blandskog med dominans av lövträd, asp,björk, ek,klibbal</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Antti Friberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Antti Friberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119447327</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Berskanten, Löftabro, Löftabro, Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>330185</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6355281</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Staren letar efter föda på gräsmattan.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Antti Friberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Antti Friberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114594546</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bergskanten, Löftabro, Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>330178</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6355294</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-02-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-02-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Besöker fågelbord.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Buskar</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>numera kalhuggen lövskog med enar. Närhet till tallar och ett område med granskog.Kontakt med ett område med tall- och blandskog.</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>enar</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Juniperus</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Juniperus</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Antti Friberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Antti Friberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>115129989</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Berskanten Frillesås, Hl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>330179</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6355272</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>En hona och hane äter från fågelmataren av och till.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Antti Friberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Antti Friberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>119447083</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Berskanten, Löftabro, Löftabro, Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>330185</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6355281</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fågeln sjunger bland lägre lövträd</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Antti Friberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Antti Friberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114594526</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bergskanten, Löftabro, Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>330178</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6355294</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-02-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-02-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Besöker fågelbord.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Antti Friberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Antti Friberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>107046060</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>lövkompost, Löftabro, Hl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>330189</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6355264</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-05-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-05-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Två kopparödleungar ligger i lövkomposten i en lövträdsdunge intill bergskanten.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Antti Friberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Antti Friberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>119446982</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kantvegetation, Kapelliden, Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>330199</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6355204</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Låg vilande I höt gräs intill ett dike.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Antti Friberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Antti Friberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43379-2022 artfynd.xlsx
+++ b/artfynd/A 43379-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2183,6 +2183,331 @@
       <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119446982</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136413950</v>
+      </c>
+      <c r="B13" t="n">
+        <v>107038</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>330267</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6355347</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Emma Håkansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Emma Håkansson, Sofia Ring</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136413950</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136413953</v>
+      </c>
+      <c r="B14" t="n">
+        <v>107038</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>330270</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6355369</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Emma Håkansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Emma Håkansson, Sofia Ring</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136413953</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136413956</v>
+      </c>
+      <c r="B15" t="n">
+        <v>107038</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>330266</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6355361</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emma Håkansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emma Håkansson, Sofia Ring</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136413956</t>
         </is>
       </c>
     </row>
@@ -2199,6 +2524,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43379-2022 artfynd.xlsx
+++ b/artfynd/A 43379-2022 artfynd.xlsx
@@ -2191,7 +2191,7 @@
         <v>136413950</v>
       </c>
       <c r="B13" t="n">
-        <v>107038</v>
+        <v>107039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>136413953</v>
       </c>
       <c r="B14" t="n">
-        <v>107038</v>
+        <v>107039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>136413956</v>
       </c>
       <c r="B15" t="n">
-        <v>107038</v>
+        <v>107039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 43379-2022 artfynd.xlsx
+++ b/artfynd/A 43379-2022 artfynd.xlsx
@@ -2191,7 +2191,7 @@
         <v>136413950</v>
       </c>
       <c r="B13" t="n">
-        <v>107039</v>
+        <v>107052</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>136413953</v>
       </c>
       <c r="B14" t="n">
-        <v>107039</v>
+        <v>107052</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>136413956</v>
       </c>
       <c r="B15" t="n">
-        <v>107039</v>
+        <v>107052</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 43379-2022 artfynd.xlsx
+++ b/artfynd/A 43379-2022 artfynd.xlsx
@@ -2191,7 +2191,7 @@
         <v>136413950</v>
       </c>
       <c r="B13" t="n">
-        <v>107052</v>
+        <v>107053</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>136413953</v>
       </c>
       <c r="B14" t="n">
-        <v>107052</v>
+        <v>107053</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>136413956</v>
       </c>
       <c r="B15" t="n">
-        <v>107052</v>
+        <v>107053</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
